--- a/outputs/Tahminlenen_Talep.xlsx
+++ b/outputs/Tahminlenen_Talep.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,8 +454,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>46153</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>8143.98</v>
@@ -479,8 +477,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>46154</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D3" t="n">
         <v>5406.81</v>
@@ -500,8 +500,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>46155</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D4" t="n">
         <v>4563.96</v>
@@ -521,8 +523,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>46156</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D5" t="n">
         <v>4144.59</v>
@@ -542,8 +546,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>46157</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D6" t="n">
         <v>3568.91</v>
@@ -563,8 +569,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>46158</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D7" t="n">
         <v>2410.13</v>
@@ -584,8 +592,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>46159</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D8" t="n">
         <v>338.06</v>
@@ -605,8 +615,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>46153</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D9" t="n">
         <v>13261.25</v>
@@ -626,8 +638,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>46154</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D10" t="n">
         <v>9309.870000000001</v>
@@ -647,8 +661,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C11" s="1" t="n">
-        <v>46155</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D11" t="n">
         <v>8478.58</v>
@@ -668,8 +684,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>46156</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D12" t="n">
         <v>8164.51</v>
@@ -689,8 +707,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C13" s="1" t="n">
-        <v>46157</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D13" t="n">
         <v>7004.57</v>
@@ -710,8 +730,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C14" s="1" t="n">
-        <v>46158</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D14" t="n">
         <v>4708.16</v>
@@ -731,8 +753,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>46159</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D15" t="n">
         <v>793.67</v>
@@ -752,8 +776,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>46153</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D16" t="n">
         <v>15072.82</v>
@@ -773,8 +799,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>46154</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D17" t="n">
         <v>10859.38</v>
@@ -794,8 +822,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C18" s="1" t="n">
-        <v>46155</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D18" t="n">
         <v>9589.809999999999</v>
@@ -815,8 +845,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n">
-        <v>46156</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D19" t="n">
         <v>9060.639999999999</v>
@@ -836,8 +868,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n">
-        <v>46157</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D20" t="n">
         <v>8354.139999999999</v>
@@ -857,8 +891,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n">
-        <v>46158</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D21" t="n">
         <v>5878.31</v>
@@ -878,8 +914,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n">
-        <v>46159</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D22" t="n">
         <v>1020.51</v>
@@ -899,8 +937,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>46153</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D23" t="n">
         <v>13222.07</v>
@@ -920,8 +960,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>46154</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D24" t="n">
         <v>9451.969999999999</v>
@@ -941,8 +983,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>46155</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D25" t="n">
         <v>8597.360000000001</v>
@@ -962,8 +1006,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C26" s="1" t="n">
-        <v>46156</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D26" t="n">
         <v>8317.91</v>
@@ -983,8 +1029,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n">
-        <v>46157</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D27" t="n">
         <v>7430.64</v>
@@ -1004,8 +1052,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C28" s="1" t="n">
-        <v>46158</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D28" t="n">
         <v>4784.89</v>
@@ -1025,8 +1075,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C29" s="1" t="n">
-        <v>46159</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D29" t="n">
         <v>763.99</v>
@@ -1046,8 +1098,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C30" s="1" t="n">
-        <v>46153</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D30" t="n">
         <v>16706.98</v>
@@ -1067,8 +1121,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C31" s="1" t="n">
-        <v>46154</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D31" t="n">
         <v>12268.54</v>
@@ -1088,8 +1144,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C32" s="1" t="n">
-        <v>46155</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D32" t="n">
         <v>11327.6</v>
@@ -1109,8 +1167,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C33" s="1" t="n">
-        <v>46156</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D33" t="n">
         <v>10460.69</v>
@@ -1130,8 +1190,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C34" s="1" t="n">
-        <v>46157</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D34" t="n">
         <v>9248.370000000001</v>
@@ -1151,8 +1213,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C35" s="1" t="n">
-        <v>46158</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D35" t="n">
         <v>6534.28</v>
@@ -1172,8 +1236,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C36" s="1" t="n">
-        <v>46159</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D36" t="n">
         <v>1287.93</v>
@@ -1193,8 +1259,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C37" s="1" t="n">
-        <v>46153</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D37" t="n">
         <v>12932.15</v>
@@ -1214,8 +1282,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C38" s="1" t="n">
-        <v>46154</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D38" t="n">
         <v>9233.780000000001</v>
@@ -1235,8 +1305,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C39" s="1" t="n">
-        <v>46155</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D39" t="n">
         <v>8429.030000000001</v>
@@ -1256,8 +1328,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C40" s="1" t="n">
-        <v>46156</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D40" t="n">
         <v>7964.98</v>
@@ -1277,8 +1351,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C41" s="1" t="n">
-        <v>46157</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D41" t="n">
         <v>7065.3</v>
@@ -1298,8 +1374,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C42" s="1" t="n">
-        <v>46158</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D42" t="n">
         <v>4715.92</v>
@@ -1319,8 +1397,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C43" s="1" t="n">
-        <v>46159</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D43" t="n">
         <v>788.4400000000001</v>
@@ -1340,8 +1420,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C44" s="1" t="n">
-        <v>46153</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D44" t="n">
         <v>9222.09</v>
@@ -1361,8 +1443,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C45" s="1" t="n">
-        <v>46154</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D45" t="n">
         <v>6438.33</v>
@@ -1382,8 +1466,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C46" s="1" t="n">
-        <v>46155</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D46" t="n">
         <v>5756.9</v>
@@ -1403,8 +1489,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C47" s="1" t="n">
-        <v>46156</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D47" t="n">
         <v>5242.59</v>
@@ -1424,8 +1512,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C48" s="1" t="n">
-        <v>46157</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D48" t="n">
         <v>4719.58</v>
@@ -1445,8 +1535,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C49" s="1" t="n">
-        <v>46158</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D49" t="n">
         <v>3061.53</v>
@@ -1466,8 +1558,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C50" s="1" t="n">
-        <v>46159</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D50" t="n">
         <v>428.28</v>
@@ -1487,8 +1581,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C51" s="1" t="n">
-        <v>46153</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D51" t="n">
         <v>10230.29</v>
@@ -1508,8 +1604,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C52" s="1" t="n">
-        <v>46154</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D52" t="n">
         <v>7236.59</v>
@@ -1529,8 +1627,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C53" s="1" t="n">
-        <v>46155</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D53" t="n">
         <v>6410.17</v>
@@ -1550,8 +1650,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C54" s="1" t="n">
-        <v>46156</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D54" t="n">
         <v>6079.6</v>
@@ -1571,8 +1673,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C55" s="1" t="n">
-        <v>46157</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D55" t="n">
         <v>5607.27</v>
@@ -1592,8 +1696,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C56" s="1" t="n">
-        <v>46158</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D56" t="n">
         <v>3614.32</v>
@@ -1613,8 +1719,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C57" s="1" t="n">
-        <v>46159</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D57" t="n">
         <v>523.21</v>
@@ -1634,8 +1742,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C58" s="1" t="n">
-        <v>46153</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D58" t="n">
         <v>11611.03</v>
@@ -1655,8 +1765,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C59" s="1" t="n">
-        <v>46154</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D59" t="n">
         <v>8037.7</v>
@@ -1676,8 +1788,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C60" s="1" t="n">
-        <v>46155</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D60" t="n">
         <v>7566.45</v>
@@ -1697,8 +1811,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C61" s="1" t="n">
-        <v>46156</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D61" t="n">
         <v>7126.59</v>
@@ -1718,8 +1834,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C62" s="1" t="n">
-        <v>46157</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D62" t="n">
         <v>6160.86</v>
@@ -1739,8 +1857,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C63" s="1" t="n">
-        <v>46158</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D63" t="n">
         <v>4169.95</v>
@@ -1760,8 +1880,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C64" s="1" t="n">
-        <v>46159</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D64" t="n">
         <v>767.78</v>
@@ -1781,8 +1903,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C65" s="1" t="n">
-        <v>46153</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D65" t="n">
         <v>8528.17</v>
@@ -1802,8 +1926,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C66" s="1" t="n">
-        <v>46154</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D66" t="n">
         <v>5660.31</v>
@@ -1823,8 +1949,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C67" s="1" t="n">
-        <v>46155</v>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D67" t="n">
         <v>5457.7</v>
@@ -1844,8 +1972,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C68" s="1" t="n">
-        <v>46156</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D68" t="n">
         <v>5017.5</v>
@@ -1865,8 +1995,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C69" s="1" t="n">
-        <v>46157</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D69" t="n">
         <v>4523.82</v>
@@ -1886,8 +2018,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C70" s="1" t="n">
-        <v>46158</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D70" t="n">
         <v>2883.5</v>
@@ -1907,8 +2041,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C71" s="1" t="n">
-        <v>46159</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D71" t="n">
         <v>476.75</v>
@@ -1928,8 +2064,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C72" s="1" t="n">
-        <v>46153</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D72" t="n">
         <v>5907.49</v>
@@ -1949,8 +2087,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C73" s="1" t="n">
-        <v>46154</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D73" t="n">
         <v>3564.88</v>
@@ -1970,8 +2110,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C74" s="1" t="n">
-        <v>46155</v>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D74" t="n">
         <v>3318.23</v>
@@ -1991,8 +2133,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C75" s="1" t="n">
-        <v>46156</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D75" t="n">
         <v>3059.49</v>
@@ -2012,8 +2156,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C76" s="1" t="n">
-        <v>46157</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D76" t="n">
         <v>2838.03</v>
@@ -2033,8 +2179,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C77" s="1" t="n">
-        <v>46158</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D77" t="n">
         <v>1706.52</v>
@@ -2054,8 +2202,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C78" s="1" t="n">
-        <v>46159</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D78" t="n">
         <v>286.79</v>
@@ -2075,8 +2225,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C79" s="1" t="n">
-        <v>46153</v>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D79" t="n">
         <v>5482.44</v>
@@ -2096,8 +2248,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C80" s="1" t="n">
-        <v>46154</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D80" t="n">
         <v>3262.44</v>
@@ -2117,8 +2271,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C81" s="1" t="n">
-        <v>46155</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D81" t="n">
         <v>3222.86</v>
@@ -2138,8 +2294,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C82" s="1" t="n">
-        <v>46156</v>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D82" t="n">
         <v>2782.9</v>
@@ -2159,8 +2317,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C83" s="1" t="n">
-        <v>46157</v>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D83" t="n">
         <v>2623.51</v>
@@ -2180,8 +2340,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C84" s="1" t="n">
-        <v>46158</v>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D84" t="n">
         <v>1679.06</v>
@@ -2201,8 +2363,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C85" s="1" t="n">
-        <v>46159</v>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D85" t="n">
         <v>284.41</v>
@@ -2222,8 +2386,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C86" s="1" t="n">
-        <v>46153</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D86" t="n">
         <v>6002.23</v>
@@ -2243,8 +2409,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C87" s="1" t="n">
-        <v>46154</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D87" t="n">
         <v>3619.49</v>
@@ -2264,8 +2432,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C88" s="1" t="n">
-        <v>46155</v>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D88" t="n">
         <v>3499.42</v>
@@ -2285,8 +2455,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C89" s="1" t="n">
-        <v>46156</v>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D89" t="n">
         <v>3057.78</v>
@@ -2306,8 +2478,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C90" s="1" t="n">
-        <v>46157</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D90" t="n">
         <v>2855.82</v>
@@ -2327,8 +2501,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C91" s="1" t="n">
-        <v>46158</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D91" t="n">
         <v>1754.59</v>
@@ -2348,8 +2524,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C92" s="1" t="n">
-        <v>46159</v>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D92" t="n">
         <v>312.65</v>
@@ -2369,8 +2547,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C93" s="1" t="n">
-        <v>46153</v>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D93" t="n">
         <v>13694.12</v>
@@ -2390,8 +2570,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C94" s="1" t="n">
-        <v>46154</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D94" t="n">
         <v>10300.9</v>
@@ -2411,8 +2593,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C95" s="1" t="n">
-        <v>46155</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D95" t="n">
         <v>9399.309999999999</v>
@@ -2432,8 +2616,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C96" s="1" t="n">
-        <v>46156</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D96" t="n">
         <v>8977.27</v>
@@ -2453,8 +2639,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C97" s="1" t="n">
-        <v>46157</v>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D97" t="n">
         <v>8092.38</v>
@@ -2474,8 +2662,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C98" s="1" t="n">
-        <v>46158</v>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D98" t="n">
         <v>5216.56</v>
@@ -2495,8 +2685,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C99" s="1" t="n">
-        <v>46159</v>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D99" t="n">
         <v>2315.52</v>
@@ -2516,8 +2708,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C100" s="1" t="n">
-        <v>46153</v>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D100" t="n">
         <v>6732.35</v>
@@ -2537,8 +2731,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C101" s="1" t="n">
-        <v>46154</v>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D101" t="n">
         <v>4182.18</v>
@@ -2558,8 +2754,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C102" s="1" t="n">
-        <v>46155</v>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D102" t="n">
         <v>3973.01</v>
@@ -2579,8 +2777,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C103" s="1" t="n">
-        <v>46156</v>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D103" t="n">
         <v>3489.01</v>
@@ -2600,8 +2800,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C104" s="1" t="n">
-        <v>46157</v>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D104" t="n">
         <v>3272.75</v>
@@ -2621,8 +2823,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C105" s="1" t="n">
-        <v>46158</v>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D105" t="n">
         <v>2019.56</v>
@@ -2642,8 +2846,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C106" s="1" t="n">
-        <v>46159</v>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D106" t="n">
         <v>371.57</v>
@@ -2663,8 +2869,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C107" s="1" t="n">
-        <v>46153</v>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D107" t="n">
         <v>7207.74</v>
@@ -2684,8 +2892,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C108" s="1" t="n">
-        <v>46154</v>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D108" t="n">
         <v>4754.61</v>
@@ -2705,8 +2915,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C109" s="1" t="n">
-        <v>46155</v>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D109" t="n">
         <v>4411.31</v>
@@ -2726,8 +2938,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C110" s="1" t="n">
-        <v>46156</v>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D110" t="n">
         <v>4076.51</v>
@@ -2747,8 +2961,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C111" s="1" t="n">
-        <v>46157</v>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D111" t="n">
         <v>3466.57</v>
@@ -2768,8 +2984,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C112" s="1" t="n">
-        <v>46158</v>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D112" t="n">
         <v>2138.61</v>
@@ -2789,8 +3007,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C113" s="1" t="n">
-        <v>46159</v>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D113" t="n">
         <v>381.28</v>
@@ -2810,8 +3030,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C114" s="1" t="n">
-        <v>46153</v>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D114" t="n">
         <v>13054.57</v>
@@ -2831,8 +3053,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C115" s="1" t="n">
-        <v>46154</v>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D115" t="n">
         <v>9380.049999999999</v>
@@ -2852,8 +3076,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C116" s="1" t="n">
-        <v>46155</v>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D116" t="n">
         <v>8623.59</v>
@@ -2873,8 +3099,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C117" s="1" t="n">
-        <v>46156</v>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D117" t="n">
         <v>8095.72</v>
@@ -2894,8 +3122,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C118" s="1" t="n">
-        <v>46157</v>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D118" t="n">
         <v>6941.2</v>
@@ -2915,8 +3145,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C119" s="1" t="n">
-        <v>46158</v>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D119" t="n">
         <v>4724.25</v>
@@ -2936,8 +3168,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C120" s="1" t="n">
-        <v>46159</v>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D120" t="n">
         <v>1030.81</v>
@@ -2957,8 +3191,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C121" s="1" t="n">
-        <v>46153</v>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D121" t="n">
         <v>18555.02</v>
@@ -2978,8 +3214,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C122" s="1" t="n">
-        <v>46154</v>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D122" t="n">
         <v>14539.39</v>
@@ -2999,8 +3237,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C123" s="1" t="n">
-        <v>46155</v>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D123" t="n">
         <v>13740.59</v>
@@ -3020,8 +3260,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C124" s="1" t="n">
-        <v>46156</v>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D124" t="n">
         <v>13129.97</v>
@@ -3041,8 +3283,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C125" s="1" t="n">
-        <v>46157</v>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D125" t="n">
         <v>11440.91</v>
@@ -3062,8 +3306,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C126" s="1" t="n">
-        <v>46158</v>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D126" t="n">
         <v>8410.639999999999</v>
@@ -3083,8 +3329,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C127" s="1" t="n">
-        <v>46159</v>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D127" t="n">
         <v>4601.27</v>
@@ -3104,8 +3352,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C128" s="1" t="n">
-        <v>46153</v>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D128" t="n">
         <v>12665.45</v>
@@ -3125,8 +3375,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C129" s="1" t="n">
-        <v>46154</v>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D129" t="n">
         <v>8944.16</v>
@@ -3146,8 +3398,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C130" s="1" t="n">
-        <v>46155</v>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D130" t="n">
         <v>8300.540000000001</v>
@@ -3167,8 +3421,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C131" s="1" t="n">
-        <v>46156</v>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D131" t="n">
         <v>7705.03</v>
@@ -3188,8 +3444,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C132" s="1" t="n">
-        <v>46157</v>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D132" t="n">
         <v>6590.24</v>
@@ -3209,8 +3467,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C133" s="1" t="n">
-        <v>46158</v>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D133" t="n">
         <v>4640.64</v>
@@ -3230,8 +3490,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C134" s="1" t="n">
-        <v>46159</v>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D134" t="n">
         <v>1060.88</v>
@@ -3251,8 +3513,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C135" s="1" t="n">
-        <v>46153</v>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D135" t="n">
         <v>7097.38</v>
@@ -3272,8 +3536,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C136" s="1" t="n">
-        <v>46154</v>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D136" t="n">
         <v>4382.19</v>
@@ -3293,8 +3559,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C137" s="1" t="n">
-        <v>46155</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D137" t="n">
         <v>3996.75</v>
@@ -3314,8 +3582,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C138" s="1" t="n">
-        <v>46156</v>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D138" t="n">
         <v>3616.36</v>
@@ -3335,8 +3605,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C139" s="1" t="n">
-        <v>46157</v>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D139" t="n">
         <v>3439.78</v>
@@ -3356,8 +3628,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C140" s="1" t="n">
-        <v>46158</v>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D140" t="n">
         <v>2152.81</v>
@@ -3377,8 +3651,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C141" s="1" t="n">
-        <v>46159</v>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D141" t="n">
         <v>386.52</v>
@@ -3398,8 +3674,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C142" s="1" t="n">
-        <v>46153</v>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D142" t="n">
         <v>31404.92</v>
@@ -3419,8 +3697,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C143" s="1" t="n">
-        <v>46154</v>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D143" t="n">
         <v>25922.52</v>
@@ -3440,8 +3720,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C144" s="1" t="n">
-        <v>46155</v>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D144" t="n">
         <v>24924.35</v>
@@ -3461,8 +3743,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C145" s="1" t="n">
-        <v>46156</v>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D145" t="n">
         <v>21972.02</v>
@@ -3482,8 +3766,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C146" s="1" t="n">
-        <v>46157</v>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D146" t="n">
         <v>20415.38</v>
@@ -3503,8 +3789,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C147" s="1" t="n">
-        <v>46158</v>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D147" t="n">
         <v>16016.02</v>
@@ -3524,8 +3812,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C148" s="1" t="n">
-        <v>46159</v>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D148" t="n">
         <v>5564.78</v>
@@ -3545,8 +3835,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C149" s="1" t="n">
-        <v>46153</v>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D149" t="n">
         <v>19555.46</v>
@@ -3566,8 +3858,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C150" s="1" t="n">
-        <v>46154</v>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D150" t="n">
         <v>15216.86</v>
@@ -3587,8 +3881,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C151" s="1" t="n">
-        <v>46155</v>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D151" t="n">
         <v>14636.86</v>
@@ -3608,8 +3904,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C152" s="1" t="n">
-        <v>46156</v>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D152" t="n">
         <v>13558.66</v>
@@ -3629,8 +3927,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C153" s="1" t="n">
-        <v>46157</v>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D153" t="n">
         <v>12626.6</v>
@@ -3650,8 +3950,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C154" s="1" t="n">
-        <v>46158</v>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D154" t="n">
         <v>9544.57</v>
@@ -3671,8 +3973,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C155" s="1" t="n">
-        <v>46159</v>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D155" t="n">
         <v>5226.96</v>
@@ -3692,8 +3996,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C156" s="1" t="n">
-        <v>46153</v>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D156" t="n">
         <v>14089.54</v>
@@ -3713,8 +4019,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C157" s="1" t="n">
-        <v>46154</v>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D157" t="n">
         <v>8779.049999999999</v>
@@ -3734,8 +4042,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C158" s="1" t="n">
-        <v>46155</v>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D158" t="n">
         <v>8574.99</v>
@@ -3755,8 +4065,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C159" s="1" t="n">
-        <v>46156</v>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D159" t="n">
         <v>8084.37</v>
@@ -3776,8 +4088,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C160" s="1" t="n">
-        <v>46157</v>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D160" t="n">
         <v>7625.78</v>
@@ -3797,8 +4111,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C161" s="1" t="n">
-        <v>46158</v>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D161" t="n">
         <v>5516.25</v>
@@ -3818,8 +4134,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C162" s="1" t="n">
-        <v>46159</v>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D162" t="n">
         <v>744.12</v>
@@ -3839,8 +4157,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C163" s="1" t="n">
-        <v>46153</v>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D163" t="n">
         <v>24329.1</v>
@@ -3860,8 +4180,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C164" s="1" t="n">
-        <v>46154</v>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D164" t="n">
         <v>18193.97</v>
@@ -3881,8 +4203,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C165" s="1" t="n">
-        <v>46155</v>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D165" t="n">
         <v>17763.78</v>
@@ -3902,8 +4226,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C166" s="1" t="n">
-        <v>46156</v>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D166" t="n">
         <v>16409.15</v>
@@ -3923,8 +4249,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C167" s="1" t="n">
-        <v>46157</v>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D167" t="n">
         <v>15163.19</v>
@@ -3944,8 +4272,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C168" s="1" t="n">
-        <v>46158</v>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D168" t="n">
         <v>11715.74</v>
@@ -3965,8 +4295,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C169" s="1" t="n">
-        <v>46159</v>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D169" t="n">
         <v>4740.98</v>
@@ -3986,8 +4318,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C170" s="1" t="n">
-        <v>46153</v>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D170" t="n">
         <v>9009.379999999999</v>
@@ -4007,8 +4341,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C171" s="1" t="n">
-        <v>46154</v>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D171" t="n">
         <v>6150.72</v>
@@ -4028,8 +4364,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C172" s="1" t="n">
-        <v>46155</v>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D172" t="n">
         <v>5790.12</v>
@@ -4049,8 +4387,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C173" s="1" t="n">
-        <v>46156</v>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D173" t="n">
         <v>5446.52</v>
@@ -4070,8 +4410,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C174" s="1" t="n">
-        <v>46157</v>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D174" t="n">
         <v>4764.65</v>
@@ -4091,8 +4433,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C175" s="1" t="n">
-        <v>46158</v>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D175" t="n">
         <v>3265.78</v>
@@ -4112,8 +4456,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C176" s="1" t="n">
-        <v>46159</v>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D176" t="n">
         <v>523.0700000000001</v>
@@ -4133,8 +4479,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C177" s="1" t="n">
-        <v>46153</v>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D177" t="n">
         <v>13120.08</v>
@@ -4154,8 +4502,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C178" s="1" t="n">
-        <v>46154</v>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D178" t="n">
         <v>9763.870000000001</v>
@@ -4175,8 +4525,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C179" s="1" t="n">
-        <v>46155</v>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D179" t="n">
         <v>8776.18</v>
@@ -4196,8 +4548,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C180" s="1" t="n">
-        <v>46156</v>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D180" t="n">
         <v>8404.959999999999</v>
@@ -4217,8 +4571,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C181" s="1" t="n">
-        <v>46157</v>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D181" t="n">
         <v>7449.04</v>
@@ -4238,8 +4594,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C182" s="1" t="n">
-        <v>46158</v>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D182" t="n">
         <v>6177.31</v>
@@ -4259,8 +4617,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C183" s="1" t="n">
-        <v>46159</v>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D183" t="n">
         <v>1364.37</v>
@@ -4280,8 +4640,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C184" s="1" t="n">
-        <v>46153</v>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D184" t="n">
         <v>21027.97</v>
@@ -4301,8 +4663,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C185" s="1" t="n">
-        <v>46154</v>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D185" t="n">
         <v>16623.53</v>
@@ -4322,8 +4686,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C186" s="1" t="n">
-        <v>46155</v>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D186" t="n">
         <v>15542.41</v>
@@ -4343,8 +4709,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C187" s="1" t="n">
-        <v>46156</v>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D187" t="n">
         <v>14572.96</v>
@@ -4364,8 +4732,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C188" s="1" t="n">
-        <v>46157</v>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D188" t="n">
         <v>13481.09</v>
@@ -4385,8 +4755,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C189" s="1" t="n">
-        <v>46158</v>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D189" t="n">
         <v>10775.76</v>
@@ -4406,8 +4778,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C190" s="1" t="n">
-        <v>46159</v>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D190" t="n">
         <v>5560.13</v>
@@ -4427,8 +4801,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C191" s="1" t="n">
-        <v>46153</v>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D191" t="n">
         <v>13529.05</v>
@@ -4448,8 +4824,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C192" s="1" t="n">
-        <v>46154</v>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D192" t="n">
         <v>9862</v>
@@ -4469,8 +4847,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C193" s="1" t="n">
-        <v>46155</v>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D193" t="n">
         <v>9042.450000000001</v>
@@ -4490,8 +4870,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C194" s="1" t="n">
-        <v>46156</v>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D194" t="n">
         <v>8432.469999999999</v>
@@ -4511,8 +4893,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C195" s="1" t="n">
-        <v>46157</v>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D195" t="n">
         <v>7696.97</v>
@@ -4532,8 +4916,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C196" s="1" t="n">
-        <v>46158</v>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D196" t="n">
         <v>6154.8</v>
@@ -4553,8 +4939,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C197" s="1" t="n">
-        <v>46159</v>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D197" t="n">
         <v>1360.22</v>
@@ -4574,8 +4962,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C198" s="1" t="n">
-        <v>46153</v>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D198" t="n">
         <v>23968.75</v>
@@ -4595,8 +4985,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C199" s="1" t="n">
-        <v>46154</v>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D199" t="n">
         <v>19015.87</v>
@@ -4616,8 +5008,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C200" s="1" t="n">
-        <v>46155</v>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D200" t="n">
         <v>16981.88</v>
@@ -4637,8 +5031,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C201" s="1" t="n">
-        <v>46156</v>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D201" t="n">
         <v>15820.5</v>
@@ -4658,8 +5054,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C202" s="1" t="n">
-        <v>46157</v>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D202" t="n">
         <v>14908.42</v>
@@ -4679,8 +5077,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C203" s="1" t="n">
-        <v>46158</v>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D203" t="n">
         <v>11648.26</v>
@@ -4700,8 +5100,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C204" s="1" t="n">
-        <v>46159</v>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D204" t="n">
         <v>5840.06</v>
@@ -4721,8 +5123,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C205" s="1" t="n">
-        <v>46153</v>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D205" t="n">
         <v>10183.87</v>
@@ -4742,8 +5146,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C206" s="1" t="n">
-        <v>46154</v>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D206" t="n">
         <v>6836.48</v>
@@ -4763,8 +5169,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C207" s="1" t="n">
-        <v>46155</v>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D207" t="n">
         <v>6296.28</v>
@@ -4784,8 +5192,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C208" s="1" t="n">
-        <v>46156</v>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D208" t="n">
         <v>5995.29</v>
@@ -4805,8 +5215,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C209" s="1" t="n">
-        <v>46157</v>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D209" t="n">
         <v>5472.16</v>
@@ -4826,8 +5238,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C210" s="1" t="n">
-        <v>46158</v>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D210" t="n">
         <v>3572.29</v>
@@ -4847,8 +5261,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C211" s="1" t="n">
-        <v>46159</v>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D211" t="n">
         <v>572.09</v>
@@ -4868,8 +5284,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C212" s="1" t="n">
-        <v>46153</v>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D212" t="n">
         <v>34232.77</v>
@@ -4889,8 +5307,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C213" s="1" t="n">
-        <v>46154</v>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D213" t="n">
         <v>28402.07</v>
@@ -4910,8 +5330,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C214" s="1" t="n">
-        <v>46155</v>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D214" t="n">
         <v>27689.76</v>
@@ -4931,8 +5353,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C215" s="1" t="n">
-        <v>46156</v>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D215" t="n">
         <v>24660.51</v>
@@ -4952,8 +5376,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C216" s="1" t="n">
-        <v>46157</v>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D216" t="n">
         <v>22186.84</v>
@@ -4973,8 +5399,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C217" s="1" t="n">
-        <v>46158</v>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D217" t="n">
         <v>16870.81</v>
@@ -4994,8 +5422,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C218" s="1" t="n">
-        <v>46159</v>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D218" t="n">
         <v>6208.14</v>
@@ -5015,8 +5445,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C219" s="1" t="n">
-        <v>46153</v>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D219" t="n">
         <v>38261.86</v>
@@ -5036,8 +5468,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C220" s="1" t="n">
-        <v>46154</v>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D220" t="n">
         <v>34418.11</v>
@@ -5057,8 +5491,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C221" s="1" t="n">
-        <v>46155</v>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D221" t="n">
         <v>33826.17</v>
@@ -5078,8 +5514,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C222" s="1" t="n">
-        <v>46156</v>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D222" t="n">
         <v>30860.16</v>
@@ -5099,8 +5537,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C223" s="1" t="n">
-        <v>46157</v>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D223" t="n">
         <v>26987.05</v>
@@ -5120,8 +5560,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C224" s="1" t="n">
-        <v>46158</v>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D224" t="n">
         <v>17934.88</v>
@@ -5141,8 +5583,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C225" s="1" t="n">
-        <v>46159</v>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D225" t="n">
         <v>7232.33</v>
@@ -5162,8 +5606,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C226" s="1" t="n">
-        <v>46153</v>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D226" t="n">
         <v>32245.37</v>
@@ -5183,8 +5629,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C227" s="1" t="n">
-        <v>46154</v>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D227" t="n">
         <v>26434.5</v>
@@ -5204,8 +5652,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C228" s="1" t="n">
-        <v>46155</v>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D228" t="n">
         <v>25405.76</v>
@@ -5225,8 +5675,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C229" s="1" t="n">
-        <v>46156</v>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D229" t="n">
         <v>23044.01</v>
@@ -5246,8 +5698,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C230" s="1" t="n">
-        <v>46157</v>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D230" t="n">
         <v>21122.36</v>
@@ -5267,8 +5721,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C231" s="1" t="n">
-        <v>46158</v>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D231" t="n">
         <v>16083.14</v>
@@ -5288,8 +5744,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C232" s="1" t="n">
-        <v>46159</v>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D232" t="n">
         <v>5481.69</v>
@@ -5309,8 +5767,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C233" s="1" t="n">
-        <v>46153</v>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D233" t="n">
         <v>16499.52</v>
@@ -5330,8 +5790,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C234" s="1" t="n">
-        <v>46154</v>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D234" t="n">
         <v>10438.36</v>
@@ -5351,8 +5813,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C235" s="1" t="n">
-        <v>46155</v>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D235" t="n">
         <v>9994.629999999999</v>
@@ -5372,8 +5836,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C236" s="1" t="n">
-        <v>46156</v>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D236" t="n">
         <v>9677.34</v>
@@ -5393,8 +5859,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C237" s="1" t="n">
-        <v>46157</v>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D237" t="n">
         <v>9103.200000000001</v>
@@ -5414,8 +5882,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C238" s="1" t="n">
-        <v>46158</v>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D238" t="n">
         <v>6779.31</v>
@@ -5435,8 +5905,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C239" s="1" t="n">
-        <v>46159</v>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D239" t="n">
         <v>758.86</v>
@@ -5456,8 +5928,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C240" s="1" t="n">
-        <v>46153</v>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D240" t="n">
         <v>5374.32</v>
@@ -5477,8 +5951,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C241" s="1" t="n">
-        <v>46154</v>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D241" t="n">
         <v>3189.62</v>
@@ -5498,8 +5974,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C242" s="1" t="n">
-        <v>46155</v>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D242" t="n">
         <v>3098.74</v>
@@ -5519,8 +5997,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C243" s="1" t="n">
-        <v>46156</v>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D243" t="n">
         <v>2717.19</v>
@@ -5540,8 +6020,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C244" s="1" t="n">
-        <v>46157</v>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D244" t="n">
         <v>2556.48</v>
@@ -5561,8 +6043,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C245" s="1" t="n">
-        <v>46158</v>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D245" t="n">
         <v>1562.1</v>
@@ -5582,8 +6066,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C246" s="1" t="n">
-        <v>46159</v>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D246" t="n">
         <v>268.54</v>
@@ -5603,8 +6089,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C247" s="1" t="n">
-        <v>46153</v>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D247" t="n">
         <v>22993.87</v>
@@ -5624,8 +6112,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C248" s="1" t="n">
-        <v>46154</v>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D248" t="n">
         <v>21690.42</v>
@@ -5645,8 +6135,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C249" s="1" t="n">
-        <v>46155</v>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D249" t="n">
         <v>19854.99</v>
@@ -5666,8 +6158,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C250" s="1" t="n">
-        <v>46156</v>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D250" t="n">
         <v>17978.22</v>
@@ -5687,8 +6181,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C251" s="1" t="n">
-        <v>46157</v>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D251" t="n">
         <v>17120.23</v>
@@ -5708,8 +6204,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C252" s="1" t="n">
-        <v>46158</v>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D252" t="n">
         <v>12399.65</v>
@@ -5729,8 +6227,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C253" s="1" t="n">
-        <v>46159</v>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D253" t="n">
         <v>7226.18</v>
@@ -5750,8 +6250,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C254" s="1" t="n">
-        <v>46153</v>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D254" t="n">
         <v>18460.15</v>
@@ -5771,8 +6273,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C255" s="1" t="n">
-        <v>46154</v>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D255" t="n">
         <v>15385.9</v>
@@ -5792,8 +6296,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C256" s="1" t="n">
-        <v>46155</v>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D256" t="n">
         <v>14438.75</v>
@@ -5813,8 +6319,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C257" s="1" t="n">
-        <v>46156</v>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D257" t="n">
         <v>13708.54</v>
@@ -5834,8 +6342,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C258" s="1" t="n">
-        <v>46157</v>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D258" t="n">
         <v>12788.84</v>
@@ -5855,8 +6365,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C259" s="1" t="n">
-        <v>46158</v>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D259" t="n">
         <v>9476.540000000001</v>
@@ -5876,8 +6388,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C260" s="1" t="n">
-        <v>46159</v>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D260" t="n">
         <v>5803.93</v>
@@ -5897,8 +6411,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C261" s="1" t="n">
-        <v>46153</v>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D261" t="n">
         <v>7793.83</v>
@@ -5918,8 +6434,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C262" s="1" t="n">
-        <v>46154</v>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D262" t="n">
         <v>5174.58</v>
@@ -5939,8 +6457,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C263" s="1" t="n">
-        <v>46155</v>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D263" t="n">
         <v>4532.69</v>
@@ -5960,8 +6480,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C264" s="1" t="n">
-        <v>46156</v>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D264" t="n">
         <v>4337.06</v>
@@ -5981,8 +6503,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C265" s="1" t="n">
-        <v>46157</v>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D265" t="n">
         <v>3926.88</v>
@@ -6002,8 +6526,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C266" s="1" t="n">
-        <v>46158</v>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D266" t="n">
         <v>2222.1</v>
@@ -6023,8 +6549,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C267" s="1" t="n">
-        <v>46159</v>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D267" t="n">
         <v>400.72</v>
@@ -6044,8 +6572,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C268" s="1" t="n">
-        <v>46153</v>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D268" t="n">
         <v>19601.96</v>
@@ -6065,8 +6595,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C269" s="1" t="n">
-        <v>46154</v>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D269" t="n">
         <v>15855.59</v>
@@ -6086,8 +6618,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C270" s="1" t="n">
-        <v>46155</v>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D270" t="n">
         <v>14441.97</v>
@@ -6107,8 +6641,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C271" s="1" t="n">
-        <v>46156</v>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D271" t="n">
         <v>13309.63</v>
@@ -6128,8 +6664,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C272" s="1" t="n">
-        <v>46157</v>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D272" t="n">
         <v>12733.74</v>
@@ -6149,8 +6687,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C273" s="1" t="n">
-        <v>46158</v>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D273" t="n">
         <v>9553.6</v>
@@ -6170,8 +6710,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C274" s="1" t="n">
-        <v>46159</v>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D274" t="n">
         <v>5570.35</v>
@@ -6191,8 +6733,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C275" s="1" t="n">
-        <v>46153</v>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D275" t="n">
         <v>17183.17</v>
@@ -6212,8 +6756,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C276" s="1" t="n">
-        <v>46154</v>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D276" t="n">
         <v>12784.54</v>
@@ -6233,8 +6779,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C277" s="1" t="n">
-        <v>46155</v>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D277" t="n">
         <v>11797.03</v>
@@ -6254,8 +6802,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C278" s="1" t="n">
-        <v>46156</v>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D278" t="n">
         <v>11020.74</v>
@@ -6275,8 +6825,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C279" s="1" t="n">
-        <v>46157</v>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D279" t="n">
         <v>9922.34</v>
@@ -6296,8 +6848,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C280" s="1" t="n">
-        <v>46158</v>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D280" t="n">
         <v>7589.88</v>
@@ -6317,8 +6871,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C281" s="1" t="n">
-        <v>46159</v>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D281" t="n">
         <v>2385.67</v>
@@ -6338,8 +6894,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C282" s="1" t="n">
-        <v>46153</v>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D282" t="n">
         <v>17100.16</v>
@@ -6359,8 +6917,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C283" s="1" t="n">
-        <v>46154</v>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D283" t="n">
         <v>13928.57</v>
@@ -6380,8 +6940,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C284" s="1" t="n">
-        <v>46155</v>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D284" t="n">
         <v>13492.67</v>
@@ -6401,8 +6963,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C285" s="1" t="n">
-        <v>46156</v>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D285" t="n">
         <v>12188.01</v>
@@ -6422,8 +6986,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C286" s="1" t="n">
-        <v>46157</v>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D286" t="n">
         <v>11039.59</v>
@@ -6443,8 +7009,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C287" s="1" t="n">
-        <v>46158</v>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D287" t="n">
         <v>8227.290000000001</v>
@@ -6464,8 +7032,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C288" s="1" t="n">
-        <v>46159</v>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D288" t="n">
         <v>4028.53</v>
@@ -6485,8 +7055,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C289" s="1" t="n">
-        <v>46153</v>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D289" t="n">
         <v>15233.87</v>
@@ -6506,8 +7078,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C290" s="1" t="n">
-        <v>46154</v>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D290" t="n">
         <v>10992.7</v>
@@ -6527,8 +7101,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C291" s="1" t="n">
-        <v>46155</v>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D291" t="n">
         <v>9517.799999999999</v>
@@ -6548,8 +7124,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C292" s="1" t="n">
-        <v>46156</v>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D292" t="n">
         <v>9000.07</v>
@@ -6569,8 +7147,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C293" s="1" t="n">
-        <v>46157</v>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D293" t="n">
         <v>8537.709999999999</v>
@@ -6590,8 +7170,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C294" s="1" t="n">
-        <v>46158</v>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D294" t="n">
         <v>6337.13</v>
@@ -6611,8 +7193,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C295" s="1" t="n">
-        <v>46159</v>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D295" t="n">
         <v>1629.66</v>
@@ -6632,8 +7216,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C296" s="1" t="n">
-        <v>46153</v>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D296" t="n">
         <v>9526.48</v>
@@ -6653,8 +7239,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C297" s="1" t="n">
-        <v>46154</v>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D297" t="n">
         <v>6021.61</v>
@@ -6674,8 +7262,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C298" s="1" t="n">
-        <v>46155</v>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D298" t="n">
         <v>5554.04</v>
@@ -6695,8 +7285,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C299" s="1" t="n">
-        <v>46156</v>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D299" t="n">
         <v>5297.85</v>
@@ -6716,8 +7308,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C300" s="1" t="n">
-        <v>46157</v>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D300" t="n">
         <v>4341</v>
@@ -6737,8 +7331,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C301" s="1" t="n">
-        <v>46158</v>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D301" t="n">
         <v>2987.89</v>
@@ -6758,8 +7354,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C302" s="1" t="n">
-        <v>46159</v>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D302" t="n">
         <v>442.15</v>
@@ -6779,8 +7377,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C303" s="1" t="n">
-        <v>46153</v>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D303" t="n">
         <v>24738.38</v>
@@ -6800,8 +7400,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C304" s="1" t="n">
-        <v>46154</v>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D304" t="n">
         <v>16024.19</v>
@@ -6821,8 +7423,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C305" s="1" t="n">
-        <v>46155</v>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D305" t="n">
         <v>15809.44</v>
@@ -6842,8 +7446,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C306" s="1" t="n">
-        <v>46156</v>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D306" t="n">
         <v>14689.12</v>
@@ -6863,8 +7469,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C307" s="1" t="n">
-        <v>46157</v>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D307" t="n">
         <v>13489.02</v>
@@ -6884,8 +7492,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C308" s="1" t="n">
-        <v>46158</v>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D308" t="n">
         <v>9143.280000000001</v>
@@ -6905,8 +7515,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C309" s="1" t="n">
-        <v>46159</v>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D309" t="n">
         <v>2040.67</v>
@@ -6926,8 +7538,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C310" s="1" t="n">
-        <v>46153</v>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D310" t="n">
         <v>32240.75</v>
@@ -6947,8 +7561,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C311" s="1" t="n">
-        <v>46154</v>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D311" t="n">
         <v>21505.75</v>
@@ -6968,8 +7584,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C312" s="1" t="n">
-        <v>46155</v>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D312" t="n">
         <v>21527.44</v>
@@ -6989,8 +7607,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C313" s="1" t="n">
-        <v>46156</v>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D313" t="n">
         <v>19570.77</v>
@@ -7010,8 +7630,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C314" s="1" t="n">
-        <v>46157</v>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D314" t="n">
         <v>18015.78</v>
@@ -7031,8 +7653,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C315" s="1" t="n">
-        <v>46158</v>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D315" t="n">
         <v>12071.97</v>
@@ -7052,8 +7676,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C316" s="1" t="n">
-        <v>46159</v>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D316" t="n">
         <v>3078.33</v>
@@ -7073,8 +7699,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C317" s="1" t="n">
-        <v>46153</v>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D317" t="n">
         <v>21663.14</v>
@@ -7094,8 +7722,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C318" s="1" t="n">
-        <v>46154</v>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D318" t="n">
         <v>14290.71</v>
@@ -7115,8 +7745,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C319" s="1" t="n">
-        <v>46155</v>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D319" t="n">
         <v>13933.95</v>
@@ -7136,8 +7768,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C320" s="1" t="n">
-        <v>46156</v>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D320" t="n">
         <v>12790.3</v>
@@ -7157,8 +7791,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C321" s="1" t="n">
-        <v>46157</v>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D321" t="n">
         <v>11871.67</v>
@@ -7178,8 +7814,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C322" s="1" t="n">
-        <v>46158</v>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D322" t="n">
         <v>8483.370000000001</v>
@@ -7199,8 +7837,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C323" s="1" t="n">
-        <v>46159</v>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D323" t="n">
         <v>2179.98</v>
@@ -7220,8 +7860,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C324" s="1" t="n">
-        <v>46153</v>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D324" t="n">
         <v>6220.51</v>
@@ -7241,8 +7883,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C325" s="1" t="n">
-        <v>46154</v>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D325" t="n">
         <v>3578.39</v>
@@ -7262,8 +7906,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C326" s="1" t="n">
-        <v>46155</v>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D326" t="n">
         <v>3251.27</v>
@@ -7283,8 +7929,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C327" s="1" t="n">
-        <v>46156</v>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D327" t="n">
         <v>3043.77</v>
@@ -7304,8 +7952,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C328" s="1" t="n">
-        <v>46157</v>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D328" t="n">
         <v>2917.4</v>
@@ -7325,8 +7975,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C329" s="1" t="n">
-        <v>46158</v>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D329" t="n">
         <v>1765.56</v>
@@ -7346,8 +7998,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C330" s="1" t="n">
-        <v>46159</v>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D330" t="n">
         <v>306.85</v>
@@ -7367,8 +8021,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C331" s="1" t="n">
-        <v>46153</v>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D331" t="n">
         <v>6127.73</v>
@@ -7388,8 +8044,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C332" s="1" t="n">
-        <v>46154</v>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D332" t="n">
         <v>3517.46</v>
@@ -7409,8 +8067,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C333" s="1" t="n">
-        <v>46155</v>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D333" t="n">
         <v>3285.92</v>
@@ -7430,8 +8090,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C334" s="1" t="n">
-        <v>46156</v>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D334" t="n">
         <v>2761.92</v>
@@ -7451,8 +8113,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C335" s="1" t="n">
-        <v>46157</v>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D335" t="n">
         <v>2818.55</v>
@@ -7472,8 +8136,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C336" s="1" t="n">
-        <v>46158</v>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D336" t="n">
         <v>1830.88</v>
@@ -7493,8 +8159,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C337" s="1" t="n">
-        <v>46159</v>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D337" t="n">
         <v>270.64</v>
@@ -7514,8 +8182,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C338" s="1" t="n">
-        <v>46153</v>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D338" t="n">
         <v>9487.5</v>
@@ -7535,8 +8205,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C339" s="1" t="n">
-        <v>46154</v>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D339" t="n">
         <v>6894.61</v>
@@ -7556,8 +8228,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C340" s="1" t="n">
-        <v>46155</v>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D340" t="n">
         <v>6295.54</v>
@@ -7577,8 +8251,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C341" s="1" t="n">
-        <v>46156</v>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D341" t="n">
         <v>5971.91</v>
@@ -7598,8 +8274,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C342" s="1" t="n">
-        <v>46157</v>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D342" t="n">
         <v>5286.38</v>
@@ -7619,8 +8297,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C343" s="1" t="n">
-        <v>46158</v>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D343" t="n">
         <v>3377.41</v>
@@ -7640,8 +8320,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C344" s="1" t="n">
-        <v>46159</v>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D344" t="n">
         <v>568.42</v>
@@ -7661,8 +8343,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C345" s="1" t="n">
-        <v>46153</v>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D345" t="n">
         <v>19840.66</v>
@@ -7682,8 +8366,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C346" s="1" t="n">
-        <v>46154</v>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D346" t="n">
         <v>15637.96</v>
@@ -7703,8 +8389,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C347" s="1" t="n">
-        <v>46155</v>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D347" t="n">
         <v>14006.23</v>
@@ -7724,8 +8412,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C348" s="1" t="n">
-        <v>46156</v>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D348" t="n">
         <v>13199.02</v>
@@ -7745,8 +8435,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C349" s="1" t="n">
-        <v>46157</v>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D349" t="n">
         <v>12357.62</v>
@@ -7766,8 +8458,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C350" s="1" t="n">
-        <v>46158</v>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D350" t="n">
         <v>8552.959999999999</v>
@@ -7787,8 +8481,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C351" s="1" t="n">
-        <v>46159</v>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D351" t="n">
         <v>2982.03</v>
@@ -7808,8 +8504,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C352" s="1" t="n">
-        <v>46153</v>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D352" t="n">
         <v>13417.62</v>
@@ -7829,8 +8527,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C353" s="1" t="n">
-        <v>46154</v>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D353" t="n">
         <v>9444.290000000001</v>
@@ -7850,8 +8550,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C354" s="1" t="n">
-        <v>46155</v>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D354" t="n">
         <v>8616.85</v>
@@ -7871,8 +8573,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C355" s="1" t="n">
-        <v>46156</v>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D355" t="n">
         <v>8222.07</v>
@@ -7892,8 +8596,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C356" s="1" t="n">
-        <v>46157</v>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D356" t="n">
         <v>7242.62</v>
@@ -7913,8 +8619,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C357" s="1" t="n">
-        <v>46158</v>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D357" t="n">
         <v>4802.68</v>
@@ -7934,8 +8642,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C358" s="1" t="n">
-        <v>46159</v>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D358" t="n">
         <v>935.1</v>
@@ -7955,8 +8665,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C359" s="1" t="n">
-        <v>46153</v>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D359" t="n">
         <v>5479.2</v>
@@ -7976,8 +8688,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C360" s="1" t="n">
-        <v>46154</v>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D360" t="n">
         <v>3467.62</v>
@@ -7997,8 +8711,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C361" s="1" t="n">
-        <v>46155</v>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D361" t="n">
         <v>3078.72</v>
@@ -8018,8 +8734,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C362" s="1" t="n">
-        <v>46156</v>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D362" t="n">
         <v>2789.68</v>
@@ -8039,8 +8757,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C363" s="1" t="n">
-        <v>46157</v>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D363" t="n">
         <v>2603.94</v>
@@ -8060,8 +8780,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C364" s="1" t="n">
-        <v>46158</v>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D364" t="n">
         <v>1584.76</v>
@@ -8081,8 +8803,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C365" s="1" t="n">
-        <v>46159</v>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D365" t="n">
         <v>253.2</v>
@@ -8102,8 +8826,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C366" s="1" t="n">
-        <v>46153</v>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D366" t="n">
         <v>20593.01</v>
@@ -8123,8 +8849,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C367" s="1" t="n">
-        <v>46154</v>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D367" t="n">
         <v>17668.28</v>
@@ -8144,8 +8872,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C368" s="1" t="n">
-        <v>46155</v>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D368" t="n">
         <v>15610.44</v>
@@ -8165,8 +8895,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C369" s="1" t="n">
-        <v>46156</v>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D369" t="n">
         <v>14887.12</v>
@@ -8186,8 +8918,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C370" s="1" t="n">
-        <v>46157</v>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D370" t="n">
         <v>13919.93</v>
@@ -8207,8 +8941,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C371" s="1" t="n">
-        <v>46158</v>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D371" t="n">
         <v>9441.700000000001</v>
@@ -8228,8 +8964,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C372" s="1" t="n">
-        <v>46159</v>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D372" t="n">
         <v>3174.24</v>
@@ -8249,8 +8987,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C373" s="1" t="n">
-        <v>46153</v>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D373" t="n">
         <v>7675.07</v>
@@ -8270,8 +9010,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C374" s="1" t="n">
-        <v>46154</v>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D374" t="n">
         <v>4817.47</v>
@@ -8291,8 +9033,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C375" s="1" t="n">
-        <v>46155</v>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D375" t="n">
         <v>4515.86</v>
@@ -8312,8 +9056,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C376" s="1" t="n">
-        <v>46156</v>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D376" t="n">
         <v>3753.48</v>
@@ -8333,8 +9079,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C377" s="1" t="n">
-        <v>46157</v>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D377" t="n">
         <v>3431.53</v>
@@ -8354,8 +9102,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C378" s="1" t="n">
-        <v>46158</v>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D378" t="n">
         <v>2342.05</v>
@@ -8375,8 +9125,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C379" s="1" t="n">
-        <v>46159</v>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D379" t="n">
         <v>327.71</v>
@@ -8396,8 +9148,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C380" s="1" t="n">
-        <v>46153</v>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D380" t="n">
         <v>6736.1</v>
@@ -8417,8 +9171,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C381" s="1" t="n">
-        <v>46154</v>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D381" t="n">
         <v>3968.98</v>
@@ -8438,8 +9194,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C382" s="1" t="n">
-        <v>46155</v>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D382" t="n">
         <v>3934.68</v>
@@ -8459,8 +9217,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C383" s="1" t="n">
-        <v>46156</v>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D383" t="n">
         <v>3078.76</v>
@@ -8480,8 +9240,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C384" s="1" t="n">
-        <v>46157</v>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D384" t="n">
         <v>3183.88</v>
@@ -8501,8 +9263,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C385" s="1" t="n">
-        <v>46158</v>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D385" t="n">
         <v>2060.92</v>
@@ -8522,8 +9286,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C386" s="1" t="n">
-        <v>46159</v>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D386" t="n">
         <v>298.42</v>
@@ -8543,8 +9309,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C387" s="1" t="n">
-        <v>46153</v>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D387" t="n">
         <v>8755.370000000001</v>
@@ -8564,8 +9332,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C388" s="1" t="n">
-        <v>46154</v>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D388" t="n">
         <v>6082.39</v>
@@ -8585,8 +9355,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C389" s="1" t="n">
-        <v>46155</v>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D389" t="n">
         <v>5519.32</v>
@@ -8606,8 +9378,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C390" s="1" t="n">
-        <v>46156</v>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D390" t="n">
         <v>5010.62</v>
@@ -8627,8 +9401,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C391" s="1" t="n">
-        <v>46157</v>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D391" t="n">
         <v>4490.65</v>
@@ -8648,8 +9424,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C392" s="1" t="n">
-        <v>46158</v>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D392" t="n">
         <v>2705.68</v>
@@ -8669,8 +9447,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C393" s="1" t="n">
-        <v>46159</v>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D393" t="n">
         <v>427.33</v>
@@ -8690,8 +9470,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C394" s="1" t="n">
-        <v>46153</v>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D394" t="n">
         <v>21227.14</v>
@@ -8711,8 +9493,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C395" s="1" t="n">
-        <v>46154</v>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D395" t="n">
         <v>17604.79</v>
@@ -8732,8 +9516,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C396" s="1" t="n">
-        <v>46155</v>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D396" t="n">
         <v>15678.41</v>
@@ -8753,8 +9539,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C397" s="1" t="n">
-        <v>46156</v>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D397" t="n">
         <v>14607.29</v>
@@ -8774,8 +9562,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C398" s="1" t="n">
-        <v>46157</v>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D398" t="n">
         <v>13674.1</v>
@@ -8795,8 +9585,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C399" s="1" t="n">
-        <v>46158</v>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D399" t="n">
         <v>9474.040000000001</v>
@@ -8816,8 +9608,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C400" s="1" t="n">
-        <v>46159</v>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D400" t="n">
         <v>3749.56</v>
@@ -8837,8 +9631,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C401" s="1" t="n">
-        <v>46153</v>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D401" t="n">
         <v>11299.22</v>
@@ -8858,8 +9654,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C402" s="1" t="n">
-        <v>46154</v>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D402" t="n">
         <v>7950.13</v>
@@ -8879,8 +9677,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C403" s="1" t="n">
-        <v>46155</v>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D403" t="n">
         <v>7276.02</v>
@@ -8900,8 +9700,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C404" s="1" t="n">
-        <v>46156</v>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D404" t="n">
         <v>6271.91</v>
@@ -8921,8 +9723,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C405" s="1" t="n">
-        <v>46157</v>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D405" t="n">
         <v>5544.54</v>
@@ -8942,8 +9746,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C406" s="1" t="n">
-        <v>46158</v>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D406" t="n">
         <v>3416.46</v>
@@ -8963,8 +9769,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C407" s="1" t="n">
-        <v>46159</v>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D407" t="n">
         <v>508.26</v>
@@ -8984,8 +9792,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C408" s="1" t="n">
-        <v>46153</v>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D408" t="n">
         <v>23533.48</v>
@@ -9005,8 +9815,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C409" s="1" t="n">
-        <v>46154</v>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D409" t="n">
         <v>22781.69</v>
@@ -9026,8 +9838,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C410" s="1" t="n">
-        <v>46155</v>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D410" t="n">
         <v>20812.77</v>
@@ -9047,8 +9861,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C411" s="1" t="n">
-        <v>46156</v>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D411" t="n">
         <v>18560.92</v>
@@ -9068,8 +9884,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C412" s="1" t="n">
-        <v>46157</v>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D412" t="n">
         <v>17737</v>
@@ -9089,8 +9907,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C413" s="1" t="n">
-        <v>46158</v>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D413" t="n">
         <v>11443.65</v>
@@ -9110,8 +9930,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C414" s="1" t="n">
-        <v>46159</v>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D414" t="n">
         <v>3991.46</v>
@@ -9131,8 +9953,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C415" s="1" t="n">
-        <v>46153</v>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D415" t="n">
         <v>6154.63</v>
@@ -9152,8 +9976,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C416" s="1" t="n">
-        <v>46154</v>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D416" t="n">
         <v>3619.06</v>
@@ -9173,8 +9999,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C417" s="1" t="n">
-        <v>46155</v>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D417" t="n">
         <v>3515.66</v>
@@ -9194,8 +10022,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C418" s="1" t="n">
-        <v>46156</v>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D418" t="n">
         <v>3234.9</v>
@@ -9215,8 +10045,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C419" s="1" t="n">
-        <v>46157</v>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D419" t="n">
         <v>2947.49</v>
@@ -9236,8 +10068,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C420" s="1" t="n">
-        <v>46158</v>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D420" t="n">
         <v>1716.51</v>
@@ -9257,8 +10091,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C421" s="1" t="n">
-        <v>46159</v>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D421" t="n">
         <v>278.37</v>
@@ -9278,8 +10114,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C422" s="1" t="n">
-        <v>46153</v>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D422" t="n">
         <v>20289.08</v>
@@ -9299,8 +10137,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C423" s="1" t="n">
-        <v>46154</v>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D423" t="n">
         <v>17290.51</v>
@@ -9320,8 +10160,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C424" s="1" t="n">
-        <v>46155</v>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D424" t="n">
         <v>15617.68</v>
@@ -9341,8 +10183,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C425" s="1" t="n">
-        <v>46156</v>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D425" t="n">
         <v>14610.78</v>
@@ -9362,8 +10206,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C426" s="1" t="n">
-        <v>46157</v>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D426" t="n">
         <v>13529.92</v>
@@ -9383,8 +10229,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C427" s="1" t="n">
-        <v>46158</v>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D427" t="n">
         <v>9321.32</v>
@@ -9404,8 +10252,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C428" s="1" t="n">
-        <v>46159</v>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D428" t="n">
         <v>3280.93</v>
@@ -9425,8 +10275,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C429" s="1" t="n">
-        <v>46153</v>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D429" t="n">
         <v>9048.1</v>
@@ -9446,8 +10298,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C430" s="1" t="n">
-        <v>46154</v>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D430" t="n">
         <v>6151.83</v>
@@ -9467,8 +10321,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C431" s="1" t="n">
-        <v>46155</v>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D431" t="n">
         <v>5334.55</v>
@@ -9488,8 +10344,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C432" s="1" t="n">
-        <v>46156</v>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D432" t="n">
         <v>5287.11</v>
@@ -9509,8 +10367,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C433" s="1" t="n">
-        <v>46157</v>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D433" t="n">
         <v>4579.07</v>
@@ -9530,8 +10390,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C434" s="1" t="n">
-        <v>46158</v>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D434" t="n">
         <v>2683.33</v>
@@ -9551,8 +10413,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C435" s="1" t="n">
-        <v>46159</v>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D435" t="n">
         <v>335.94</v>
@@ -9572,8 +10436,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C436" s="1" t="n">
-        <v>46153</v>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D436" t="n">
         <v>22395.36</v>
@@ -9593,8 +10459,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C437" s="1" t="n">
-        <v>46154</v>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D437" t="n">
         <v>20923.28</v>
@@ -9614,8 +10482,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C438" s="1" t="n">
-        <v>46155</v>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D438" t="n">
         <v>17888.41</v>
@@ -9635,8 +10505,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C439" s="1" t="n">
-        <v>46156</v>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D439" t="n">
         <v>18169.75</v>
@@ -9656,8 +10528,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C440" s="1" t="n">
-        <v>46157</v>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D440" t="n">
         <v>17071.22</v>
@@ -9677,8 +10551,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C441" s="1" t="n">
-        <v>46158</v>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D441" t="n">
         <v>11004.09</v>
@@ -9698,8 +10574,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C442" s="1" t="n">
-        <v>46159</v>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D442" t="n">
         <v>3507.54</v>
@@ -9719,8 +10597,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C443" s="1" t="n">
-        <v>46153</v>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D443" t="n">
         <v>17303.08</v>
@@ -9740,8 +10620,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C444" s="1" t="n">
-        <v>46154</v>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D444" t="n">
         <v>12269.58</v>
@@ -9761,8 +10643,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C445" s="1" t="n">
-        <v>46155</v>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D445" t="n">
         <v>11249.83</v>
@@ -9782,8 +10666,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C446" s="1" t="n">
-        <v>46156</v>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D446" t="n">
         <v>10938.38</v>
@@ -9803,8 +10689,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C447" s="1" t="n">
-        <v>46157</v>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D447" t="n">
         <v>9524.280000000001</v>
@@ -9824,8 +10712,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C448" s="1" t="n">
-        <v>46158</v>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D448" t="n">
         <v>6885.6</v>
@@ -9845,8 +10735,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C449" s="1" t="n">
-        <v>46159</v>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D449" t="n">
         <v>1268.53</v>
@@ -9866,8 +10758,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C450" s="1" t="n">
-        <v>46153</v>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D450" t="n">
         <v>26297.81</v>
@@ -9887,8 +10781,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C451" s="1" t="n">
-        <v>46154</v>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D451" t="n">
         <v>23806.87</v>
@@ -9908,8 +10804,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C452" s="1" t="n">
-        <v>46155</v>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D452" t="n">
         <v>23971.41</v>
@@ -9929,8 +10827,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C453" s="1" t="n">
-        <v>46156</v>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D453" t="n">
         <v>21406.22</v>
@@ -9950,8 +10850,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C454" s="1" t="n">
-        <v>46157</v>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D454" t="n">
         <v>21630.6</v>
@@ -9971,8 +10873,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C455" s="1" t="n">
-        <v>46158</v>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D455" t="n">
         <v>13554.33</v>
@@ -9992,8 +10896,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C456" s="1" t="n">
-        <v>46159</v>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D456" t="n">
         <v>4312.87</v>
@@ -10013,8 +10919,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C457" s="1" t="n">
-        <v>46153</v>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D457" t="n">
         <v>11579.74</v>
@@ -10034,8 +10942,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C458" s="1" t="n">
-        <v>46154</v>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D458" t="n">
         <v>7714.49</v>
@@ -10055,8 +10965,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C459" s="1" t="n">
-        <v>46155</v>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D459" t="n">
         <v>7396.63</v>
@@ -10076,8 +10988,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C460" s="1" t="n">
-        <v>46156</v>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D460" t="n">
         <v>7221.87</v>
@@ -10097,8 +11011,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C461" s="1" t="n">
-        <v>46157</v>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D461" t="n">
         <v>6360.02</v>
@@ -10118,8 +11034,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C462" s="1" t="n">
-        <v>46158</v>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D462" t="n">
         <v>4308.2</v>
@@ -10139,8 +11057,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C463" s="1" t="n">
-        <v>46159</v>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D463" t="n">
         <v>707.09</v>
@@ -10160,8 +11080,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C464" s="1" t="n">
-        <v>46153</v>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D464" t="n">
         <v>23781.87</v>
@@ -10181,8 +11103,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C465" s="1" t="n">
-        <v>46154</v>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D465" t="n">
         <v>23450.21</v>
@@ -10202,8 +11126,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C466" s="1" t="n">
-        <v>46155</v>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D466" t="n">
         <v>21174.55</v>
@@ -10223,8 +11149,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C467" s="1" t="n">
-        <v>46156</v>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D467" t="n">
         <v>20056.3</v>
@@ -10244,8 +11172,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C468" s="1" t="n">
-        <v>46157</v>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D468" t="n">
         <v>18014.07</v>
@@ -10265,8 +11195,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C469" s="1" t="n">
-        <v>46158</v>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D469" t="n">
         <v>12144.89</v>
@@ -10286,8 +11218,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C470" s="1" t="n">
-        <v>46159</v>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D470" t="n">
         <v>3672.05</v>
@@ -10307,8 +11241,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C471" s="1" t="n">
-        <v>46153</v>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D471" t="n">
         <v>16179.84</v>
@@ -10328,8 +11264,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C472" s="1" t="n">
-        <v>46154</v>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D472" t="n">
         <v>11655.19</v>
@@ -10349,8 +11287,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C473" s="1" t="n">
-        <v>46155</v>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D473" t="n">
         <v>10474.78</v>
@@ -10370,8 +11310,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C474" s="1" t="n">
-        <v>46156</v>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D474" t="n">
         <v>9538.110000000001</v>
@@ -10391,8 +11333,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C475" s="1" t="n">
-        <v>46157</v>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D475" t="n">
         <v>8756.290000000001</v>
@@ -10412,8 +11356,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C476" s="1" t="n">
-        <v>46158</v>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D476" t="n">
         <v>6251.18</v>
@@ -10433,8 +11379,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C477" s="1" t="n">
-        <v>46159</v>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D477" t="n">
         <v>1044.33</v>
@@ -10454,8 +11402,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C478" s="1" t="n">
-        <v>46153</v>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D478" t="n">
         <v>25247.55</v>
@@ -10475,8 +11425,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C479" s="1" t="n">
-        <v>46154</v>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D479" t="n">
         <v>23962.82</v>
@@ -10496,8 +11448,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C480" s="1" t="n">
-        <v>46155</v>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D480" t="n">
         <v>23579.86</v>
@@ -10517,8 +11471,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C481" s="1" t="n">
-        <v>46156</v>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D481" t="n">
         <v>21320.72</v>
@@ -10538,8 +11494,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C482" s="1" t="n">
-        <v>46157</v>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D482" t="n">
         <v>20921.41</v>
@@ -10559,8 +11517,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C483" s="1" t="n">
-        <v>46158</v>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D483" t="n">
         <v>13550.34</v>
@@ -10580,8 +11540,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C484" s="1" t="n">
-        <v>46159</v>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D484" t="n">
         <v>4309.54</v>
@@ -10601,8 +11563,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C485" s="1" t="n">
-        <v>46153</v>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D485" t="n">
         <v>24368.72</v>
@@ -10622,8 +11586,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C486" s="1" t="n">
-        <v>46154</v>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D486" t="n">
         <v>23432.38</v>
@@ -10643,8 +11609,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C487" s="1" t="n">
-        <v>46155</v>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D487" t="n">
         <v>22172.49</v>
@@ -10664,8 +11632,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C488" s="1" t="n">
-        <v>46156</v>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D488" t="n">
         <v>21132.57</v>
@@ -10685,8 +11655,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C489" s="1" t="n">
-        <v>46157</v>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D489" t="n">
         <v>19854.95</v>
@@ -10706,8 +11678,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C490" s="1" t="n">
-        <v>46158</v>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D490" t="n">
         <v>12906.33</v>
@@ -10727,8 +11701,10 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="C491" s="1" t="n">
-        <v>46159</v>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D491" t="n">
         <v>3737.02</v>
@@ -10748,8 +11724,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C492" s="1" t="n">
-        <v>46153</v>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D492" t="n">
         <v>30698.01</v>
@@ -10769,8 +11747,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C493" s="1" t="n">
-        <v>46154</v>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D493" t="n">
         <v>29520.51</v>
@@ -10790,8 +11770,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C494" s="1" t="n">
-        <v>46155</v>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D494" t="n">
         <v>29519.64</v>
@@ -10811,8 +11793,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C495" s="1" t="n">
-        <v>46156</v>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D495" t="n">
         <v>27349.7</v>
@@ -10832,8 +11816,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C496" s="1" t="n">
-        <v>46157</v>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D496" t="n">
         <v>26651.78</v>
@@ -10853,8 +11839,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C497" s="1" t="n">
-        <v>46158</v>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D497" t="n">
         <v>17712.37</v>
@@ -10874,8 +11862,10 @@
           <t>Balıkesir</t>
         </is>
       </c>
-      <c r="C498" s="1" t="n">
-        <v>46159</v>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D498" t="n">
         <v>5496.03</v>
@@ -10895,8 +11885,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C499" s="1" t="n">
-        <v>46153</v>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D499" t="n">
         <v>21891.14</v>
@@ -10916,8 +11908,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C500" s="1" t="n">
-        <v>46154</v>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D500" t="n">
         <v>18974.86</v>
@@ -10937,8 +11931,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C501" s="1" t="n">
-        <v>46155</v>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D501" t="n">
         <v>17785.76</v>
@@ -10958,8 +11954,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C502" s="1" t="n">
-        <v>46156</v>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D502" t="n">
         <v>16221.04</v>
@@ -10979,8 +11977,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C503" s="1" t="n">
-        <v>46157</v>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D503" t="n">
         <v>15845.13</v>
@@ -11000,8 +12000,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C504" s="1" t="n">
-        <v>46158</v>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D504" t="n">
         <v>10991.68</v>
@@ -11021,8 +12023,10 @@
           <t>Bilecik</t>
         </is>
       </c>
-      <c r="C505" s="1" t="n">
-        <v>46159</v>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D505" t="n">
         <v>4216.5</v>
@@ -11042,8 +12046,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C506" s="1" t="n">
-        <v>46153</v>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D506" t="n">
         <v>10462.19</v>
@@ -11063,8 +12069,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C507" s="1" t="n">
-        <v>46154</v>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D507" t="n">
         <v>7431.55</v>
@@ -11084,8 +12092,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C508" s="1" t="n">
-        <v>46155</v>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D508" t="n">
         <v>7679.21</v>
@@ -11105,8 +12115,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C509" s="1" t="n">
-        <v>46156</v>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D509" t="n">
         <v>7119.83</v>
@@ -11126,8 +12138,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C510" s="1" t="n">
-        <v>46157</v>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D510" t="n">
         <v>6268.33</v>
@@ -11147,8 +12161,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C511" s="1" t="n">
-        <v>46158</v>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D511" t="n">
         <v>4198.08</v>
@@ -11168,8 +12184,10 @@
           <t>Denizli</t>
         </is>
       </c>
-      <c r="C512" s="1" t="n">
-        <v>46159</v>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D512" t="n">
         <v>757.58</v>
@@ -11189,8 +12207,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C513" s="1" t="n">
-        <v>46153</v>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D513" t="n">
         <v>16716.48</v>
@@ -11210,8 +12230,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C514" s="1" t="n">
-        <v>46154</v>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D514" t="n">
         <v>14222.5</v>
@@ -11231,8 +12253,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C515" s="1" t="n">
-        <v>46155</v>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D515" t="n">
         <v>12850.54</v>
@@ -11252,8 +12276,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C516" s="1" t="n">
-        <v>46156</v>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D516" t="n">
         <v>11916.59</v>
@@ -11273,8 +12299,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C517" s="1" t="n">
-        <v>46157</v>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D517" t="n">
         <v>10653.15</v>
@@ -11294,8 +12322,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C518" s="1" t="n">
-        <v>46158</v>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D518" t="n">
         <v>7692.94</v>
@@ -11315,8 +12345,10 @@
           <t>Erzincan</t>
         </is>
       </c>
-      <c r="C519" s="1" t="n">
-        <v>46159</v>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D519" t="n">
         <v>2931.39</v>
@@ -11336,8 +12368,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C520" s="1" t="n">
-        <v>46153</v>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D520" t="n">
         <v>30575.38</v>
@@ -11357,8 +12391,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C521" s="1" t="n">
-        <v>46154</v>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D521" t="n">
         <v>29536.86</v>
@@ -11378,8 +12414,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C522" s="1" t="n">
-        <v>46155</v>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D522" t="n">
         <v>28711.91</v>
@@ -11399,8 +12437,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C523" s="1" t="n">
-        <v>46156</v>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D523" t="n">
         <v>27417.68</v>
@@ -11420,8 +12460,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C524" s="1" t="n">
-        <v>46157</v>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D524" t="n">
         <v>26479.79</v>
@@ -11441,8 +12483,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C525" s="1" t="n">
-        <v>46158</v>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D525" t="n">
         <v>17126.32</v>
@@ -11462,8 +12506,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C526" s="1" t="n">
-        <v>46159</v>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D526" t="n">
         <v>5493.99</v>
@@ -11483,8 +12529,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C527" s="1" t="n">
-        <v>46153</v>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D527" t="n">
         <v>16993.56</v>
@@ -11504,8 +12552,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C528" s="1" t="n">
-        <v>46154</v>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D528" t="n">
         <v>10610.37</v>
@@ -11525,8 +12575,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C529" s="1" t="n">
-        <v>46155</v>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D529" t="n">
         <v>10390.38</v>
@@ -11546,8 +12598,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C530" s="1" t="n">
-        <v>46156</v>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D530" t="n">
         <v>10338.47</v>
@@ -11567,8 +12621,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C531" s="1" t="n">
-        <v>46157</v>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D531" t="n">
         <v>9208.540000000001</v>
@@ -11588,8 +12644,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C532" s="1" t="n">
-        <v>46158</v>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D532" t="n">
         <v>6676.78</v>
@@ -11609,8 +12667,10 @@
           <t>Isparta</t>
         </is>
       </c>
-      <c r="C533" s="1" t="n">
-        <v>46159</v>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D533" t="n">
         <v>817.6</v>
@@ -11630,8 +12690,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C534" s="1" t="n">
-        <v>46153</v>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D534" t="n">
         <v>11128.21</v>
@@ -11651,8 +12713,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C535" s="1" t="n">
-        <v>46154</v>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D535" t="n">
         <v>7170.56</v>
@@ -11672,8 +12736,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C536" s="1" t="n">
-        <v>46155</v>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D536" t="n">
         <v>7309.72</v>
@@ -11693,8 +12759,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C537" s="1" t="n">
-        <v>46156</v>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D537" t="n">
         <v>6921.15</v>
@@ -11714,8 +12782,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C538" s="1" t="n">
-        <v>46157</v>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D538" t="n">
         <v>6489.54</v>
@@ -11735,8 +12805,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C539" s="1" t="n">
-        <v>46158</v>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D539" t="n">
         <v>4372.34</v>
@@ -11756,8 +12828,10 @@
           <t>Karaman</t>
         </is>
       </c>
-      <c r="C540" s="1" t="n">
-        <v>46159</v>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D540" t="n">
         <v>564.01</v>
@@ -11777,8 +12851,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C541" s="1" t="n">
-        <v>46153</v>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D541" t="n">
         <v>20501.36</v>
@@ -11798,8 +12874,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C542" s="1" t="n">
-        <v>46154</v>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D542" t="n">
         <v>14848.61</v>
@@ -11819,8 +12897,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C543" s="1" t="n">
-        <v>46155</v>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D543" t="n">
         <v>13694.59</v>
@@ -11840,8 +12920,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C544" s="1" t="n">
-        <v>46156</v>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D544" t="n">
         <v>13150.44</v>
@@ -11861,8 +12943,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C545" s="1" t="n">
-        <v>46157</v>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D545" t="n">
         <v>12080.31</v>
@@ -11882,8 +12966,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C546" s="1" t="n">
-        <v>46158</v>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D546" t="n">
         <v>8805.92</v>
@@ -11903,8 +12989,10 @@
           <t>Kütahya</t>
         </is>
       </c>
-      <c r="C547" s="1" t="n">
-        <v>46159</v>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D547" t="n">
         <v>2077.33</v>
@@ -11924,8 +13012,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C548" s="1" t="n">
-        <v>46153</v>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D548" t="n">
         <v>30897.57</v>
@@ -11945,8 +13035,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C549" s="1" t="n">
-        <v>46154</v>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D549" t="n">
         <v>31075.94</v>
@@ -11966,8 +13058,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C550" s="1" t="n">
-        <v>46155</v>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D550" t="n">
         <v>29551.78</v>
@@ -11987,8 +13081,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C551" s="1" t="n">
-        <v>46156</v>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D551" t="n">
         <v>27786.92</v>
@@ -12008,8 +13104,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C552" s="1" t="n">
-        <v>46157</v>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D552" t="n">
         <v>27198.87</v>
@@ -12029,8 +13127,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C553" s="1" t="n">
-        <v>46158</v>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D553" t="n">
         <v>18826.66</v>
@@ -12050,8 +13150,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C554" s="1" t="n">
-        <v>46159</v>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D554" t="n">
         <v>5751.14</v>
@@ -12071,8 +13173,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C555" s="1" t="n">
-        <v>46153</v>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D555" t="n">
         <v>21186.6</v>
@@ -12092,8 +13196,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C556" s="1" t="n">
-        <v>46154</v>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D556" t="n">
         <v>14832.36</v>
@@ -12113,8 +13219,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C557" s="1" t="n">
-        <v>46155</v>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D557" t="n">
         <v>13613.37</v>
@@ -12134,8 +13242,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C558" s="1" t="n">
-        <v>46156</v>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D558" t="n">
         <v>12908.67</v>
@@ -12155,8 +13265,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C559" s="1" t="n">
-        <v>46157</v>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D559" t="n">
         <v>11700.37</v>
@@ -12176,8 +13288,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C560" s="1" t="n">
-        <v>46158</v>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D560" t="n">
         <v>8691.780000000001</v>
@@ -12197,8 +13311,10 @@
           <t>Mardin</t>
         </is>
       </c>
-      <c r="C561" s="1" t="n">
-        <v>46159</v>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D561" t="n">
         <v>2422.35</v>
@@ -12218,8 +13334,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C562" s="1" t="n">
-        <v>46153</v>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D562" t="n">
         <v>22862.15</v>
@@ -12239,8 +13357,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C563" s="1" t="n">
-        <v>46154</v>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D563" t="n">
         <v>20347.82</v>
@@ -12260,8 +13380,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C564" s="1" t="n">
-        <v>46155</v>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D564" t="n">
         <v>18915.44</v>
@@ -12281,8 +13403,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C565" s="1" t="n">
-        <v>46156</v>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D565" t="n">
         <v>18460.72</v>
@@ -12302,8 +13426,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C566" s="1" t="n">
-        <v>46157</v>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D566" t="n">
         <v>16878.54</v>
@@ -12323,8 +13449,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C567" s="1" t="n">
-        <v>46158</v>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D567" t="n">
         <v>11943.22</v>
@@ -12344,8 +13472,10 @@
           <t>Mersin</t>
         </is>
       </c>
-      <c r="C568" s="1" t="n">
-        <v>46159</v>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D568" t="n">
         <v>4390.6</v>
@@ -12365,8 +13495,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C569" s="1" t="n">
-        <v>46153</v>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D569" t="n">
         <v>17229.47</v>
@@ -12386,8 +13518,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C570" s="1" t="n">
-        <v>46154</v>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D570" t="n">
         <v>12475.17</v>
@@ -12407,8 +13541,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C571" s="1" t="n">
-        <v>46155</v>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D571" t="n">
         <v>11379.84</v>
@@ -12428,8 +13564,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C572" s="1" t="n">
-        <v>46156</v>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D572" t="n">
         <v>10660.79</v>
@@ -12449,8 +13587,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C573" s="1" t="n">
-        <v>46157</v>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D573" t="n">
         <v>9894.290000000001</v>
@@ -12470,8 +13610,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C574" s="1" t="n">
-        <v>46158</v>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D574" t="n">
         <v>7212.74</v>
@@ -12491,8 +13633,10 @@
           <t>Sivas</t>
         </is>
       </c>
-      <c r="C575" s="1" t="n">
-        <v>46159</v>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D575" t="n">
         <v>1465.15</v>
@@ -12512,8 +13656,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C576" s="1" t="n">
-        <v>46153</v>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D576" t="n">
         <v>27082.46</v>
@@ -12533,8 +13679,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C577" s="1" t="n">
-        <v>46154</v>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D577" t="n">
         <v>25948.19</v>
@@ -12554,8 +13702,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C578" s="1" t="n">
-        <v>46155</v>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D578" t="n">
         <v>24983.82</v>
@@ -12575,8 +13725,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C579" s="1" t="n">
-        <v>46156</v>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D579" t="n">
         <v>23509.05</v>
@@ -12596,8 +13748,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C580" s="1" t="n">
-        <v>46157</v>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D580" t="n">
         <v>21633.06</v>
@@ -12617,8 +13771,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C581" s="1" t="n">
-        <v>46158</v>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D581" t="n">
         <v>14944.97</v>
@@ -12638,8 +13794,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C582" s="1" t="n">
-        <v>46159</v>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D582" t="n">
         <v>4887.25</v>
@@ -12659,8 +13817,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C583" s="1" t="n">
-        <v>46153</v>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D583" t="n">
         <v>30423.28</v>
@@ -12680,8 +13840,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C584" s="1" t="n">
-        <v>46154</v>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D584" t="n">
         <v>30143</v>
@@ -12701,8 +13863,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C585" s="1" t="n">
-        <v>46155</v>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D585" t="n">
         <v>28573.69</v>
@@ -12722,8 +13886,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C586" s="1" t="n">
-        <v>46156</v>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D586" t="n">
         <v>27722.45</v>
@@ -12743,8 +13909,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C587" s="1" t="n">
-        <v>46157</v>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D587" t="n">
         <v>26140.86</v>
@@ -12764,8 +13932,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C588" s="1" t="n">
-        <v>46158</v>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D588" t="n">
         <v>17180.83</v>
@@ -12785,8 +13955,10 @@
           <t>Yalova</t>
         </is>
       </c>
-      <c r="C589" s="1" t="n">
-        <v>46159</v>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D589" t="n">
         <v>5676.9</v>
@@ -12806,8 +13978,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C590" s="1" t="n">
-        <v>46153</v>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D590" t="n">
         <v>15898.58</v>
@@ -12827,8 +14001,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C591" s="1" t="n">
-        <v>46154</v>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D591" t="n">
         <v>11182.02</v>
@@ -12848,8 +14024,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C592" s="1" t="n">
-        <v>46155</v>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D592" t="n">
         <v>9526.32</v>
@@ -12869,8 +14047,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C593" s="1" t="n">
-        <v>46156</v>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D593" t="n">
         <v>9329.07</v>
@@ -12890,8 +14070,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C594" s="1" t="n">
-        <v>46157</v>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D594" t="n">
         <v>8753.93</v>
@@ -12911,8 +14093,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C595" s="1" t="n">
-        <v>46158</v>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D595" t="n">
         <v>6446.98</v>
@@ -12932,8 +14116,10 @@
           <t>Zonguldak</t>
         </is>
       </c>
-      <c r="C596" s="1" t="n">
-        <v>46159</v>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D596" t="n">
         <v>1173.38</v>
@@ -12953,8 +14139,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C597" s="1" t="n">
-        <v>46153</v>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D597" t="n">
         <v>19648.79</v>
@@ -12974,8 +14162,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C598" s="1" t="n">
-        <v>46154</v>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D598" t="n">
         <v>14144.91</v>
@@ -12995,8 +14185,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C599" s="1" t="n">
-        <v>46155</v>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D599" t="n">
         <v>13228.52</v>
@@ -13016,8 +14208,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C600" s="1" t="n">
-        <v>46156</v>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D600" t="n">
         <v>12483.06</v>
@@ -13037,8 +14231,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C601" s="1" t="n">
-        <v>46157</v>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D601" t="n">
         <v>11287.13</v>
@@ -13058,8 +14254,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C602" s="1" t="n">
-        <v>46158</v>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D602" t="n">
         <v>8163.49</v>
@@ -13079,8 +14277,10 @@
           <t>Şanlıurfa</t>
         </is>
       </c>
-      <c r="C603" s="1" t="n">
-        <v>46159</v>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D603" t="n">
         <v>2327.66</v>
@@ -13100,8 +14300,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C604" s="1" t="n">
-        <v>46153</v>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D604" t="n">
         <v>8096.05</v>
@@ -13121,8 +14323,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C605" s="1" t="n">
-        <v>46154</v>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D605" t="n">
         <v>5167.72</v>
@@ -13142,8 +14346,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C606" s="1" t="n">
-        <v>46155</v>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D606" t="n">
         <v>4768.04</v>
@@ -13163,8 +14369,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C607" s="1" t="n">
-        <v>46156</v>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D607" t="n">
         <v>4155.4</v>
@@ -13184,8 +14392,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C608" s="1" t="n">
-        <v>46157</v>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D608" t="n">
         <v>3774.76</v>
@@ -13205,8 +14415,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C609" s="1" t="n">
-        <v>46158</v>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D609" t="n">
         <v>2615.61</v>
@@ -13226,8 +14438,10 @@
           <t>Eskişehir</t>
         </is>
       </c>
-      <c r="C610" s="1" t="n">
-        <v>46159</v>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D610" t="n">
         <v>355.57</v>
@@ -13247,8 +14461,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C611" s="1" t="n">
-        <v>46153</v>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D611" t="n">
         <v>9140.17</v>
@@ -13268,8 +14484,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C612" s="1" t="n">
-        <v>46154</v>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D612" t="n">
         <v>5614.25</v>
@@ -13289,8 +14507,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C613" s="1" t="n">
-        <v>46155</v>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D613" t="n">
         <v>5387.88</v>
@@ -13310,8 +14530,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C614" s="1" t="n">
-        <v>46156</v>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D614" t="n">
         <v>4392.15</v>
@@ -13331,8 +14553,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C615" s="1" t="n">
-        <v>46157</v>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D615" t="n">
         <v>4091.27</v>
@@ -13352,8 +14576,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C616" s="1" t="n">
-        <v>46158</v>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D616" t="n">
         <v>2525.86</v>
@@ -13373,8 +14599,10 @@
           <t>Manisa</t>
         </is>
       </c>
-      <c r="C617" s="1" t="n">
-        <v>46159</v>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D617" t="n">
         <v>364.2</v>
@@ -13394,8 +14622,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C618" s="1" t="n">
-        <v>46153</v>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="D618" t="n">
         <v>8319.219999999999</v>
@@ -13415,8 +14645,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C619" s="1" t="n">
-        <v>46154</v>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="D619" t="n">
         <v>5269.57</v>
@@ -13436,8 +14668,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C620" s="1" t="n">
-        <v>46155</v>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="D620" t="n">
         <v>4871.06</v>
@@ -13457,8 +14691,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C621" s="1" t="n">
-        <v>46156</v>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="D621" t="n">
         <v>4134.85</v>
@@ -13478,8 +14714,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C622" s="1" t="n">
-        <v>46157</v>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="D622" t="n">
         <v>3790.22</v>
@@ -13499,8 +14737,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C623" s="1" t="n">
-        <v>46158</v>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="D623" t="n">
         <v>2494.33</v>
@@ -13520,8 +14760,10 @@
           <t>Tekirdağ</t>
         </is>
       </c>
-      <c r="C624" s="1" t="n">
-        <v>46159</v>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="D624" t="n">
         <v>351.68</v>
